--- a/source_data/workbooks/Source_Data_ED_Fig7.xlsx
+++ b/source_data/workbooks/Source_Data_ED_Fig7.xlsx
@@ -7,18 +7,21 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="ED Fig. 7a,b" sheetId="1" r:id="rId1"/>
-    <sheet name="ED Fig. 7d,e" sheetId="2" r:id="rId2"/>
-    <sheet name="ED Fig. 7g,h,i" sheetId="3" r:id="rId3"/>
-    <sheet name="ED Fig. 7j" sheetId="4" r:id="rId4"/>
-    <sheet name="ED Fig. 7k" sheetId="5" r:id="rId5"/>
+    <sheet name="ED Fig. 7a" sheetId="1" r:id="rId1"/>
+    <sheet name="ED Fig. 7b" sheetId="2" r:id="rId2"/>
+    <sheet name="ED Fig. 7d" sheetId="3" r:id="rId3"/>
+    <sheet name="ED Fig. 7e" sheetId="4" r:id="rId4"/>
+    <sheet name="ED Fig. 7g,h" sheetId="5" r:id="rId5"/>
+    <sheet name="ED Fig. 7i" sheetId="6" r:id="rId6"/>
+    <sheet name="ED Fig. 7j" sheetId="7" r:id="rId7"/>
+    <sheet name="ED Fig. 7k" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1019" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="177">
   <si>
     <t>plot_order</t>
   </si>
@@ -86,7 +89,7 @@
     <t>run5</t>
   </si>
   <si>
-    <t>Extended Data 7a,b</t>
+    <t>Extended Data 7a</t>
   </si>
   <si>
     <t>Neoplastic cell quantification, cross platform</t>
@@ -122,13 +125,10 @@
     <t>NOVA</t>
   </si>
   <si>
-    <t>TLAgent-removing knowledge</t>
-  </si>
-  <si>
-    <t>TLAgent</t>
-  </si>
-  <si>
-    <t>reference</t>
+    <t>TissueLab</t>
+  </si>
+  <si>
+    <t>Ground truth</t>
   </si>
   <si>
     <t>answer</t>
@@ -149,13 +149,13 @@
     <t>no evaluable output</t>
   </si>
   <si>
-    <t>0.0022</t>
+    <t>0.0004</t>
   </si>
   <si>
     <t>569.0</t>
   </si>
   <si>
-    <t>0.0907</t>
+    <t>0.0726</t>
   </si>
   <si>
     <t>23759.5</t>
@@ -179,25 +179,43 @@
     <t>3877233.0</t>
   </si>
   <si>
+    <t>0.9693</t>
+  </si>
+  <si>
+    <t>253870.0</t>
+  </si>
+  <si>
+    <t>261905.0</t>
+  </si>
+  <si>
+    <t>n.a. single specimen</t>
+  </si>
+  <si>
+    <t>Extended Data 7b</t>
+  </si>
+  <si>
+    <t>Neoplastic cell quantification, before and after co-evolution</t>
+  </si>
+  <si>
+    <t>Visium HD colon, one section</t>
+  </si>
+  <si>
+    <t>w/o knowledge</t>
+  </si>
+  <si>
+    <t>w/ knowledge</t>
+  </si>
+  <si>
+    <t>0.0003</t>
+  </si>
+  <si>
+    <t>0.9487</t>
+  </si>
+  <si>
     <t>0.0017</t>
   </si>
   <si>
-    <t>433.0</t>
-  </si>
-  <si>
-    <t>0.9693</t>
-  </si>
-  <si>
-    <t>253870.0</t>
-  </si>
-  <si>
-    <t>261905.0</t>
-  </si>
-  <si>
-    <t>n.a. single specimen</t>
-  </si>
-  <si>
-    <t>Extended Data 7d,e</t>
+    <t>Extended Data 7d</t>
   </si>
   <si>
     <t>Normal duct cell proportion, cross platform</t>
@@ -236,7 +254,7 @@
     <t>8.76</t>
   </si>
   <si>
-    <t>0.0016</t>
+    <t>0.0013</t>
   </si>
   <si>
     <t>0.075</t>
@@ -248,9 +266,6 @@
     <t>2.714</t>
   </si>
   <si>
-    <t>0.0</t>
-  </si>
-  <si>
     <t>0.8927</t>
   </si>
   <si>
@@ -260,7 +275,22 @@
     <t>47.15</t>
   </si>
   <si>
-    <t>Extended Data 7g,h,i</t>
+    <t>Extended Data 7e</t>
+  </si>
+  <si>
+    <t>Normal duct cell proportion, before and after co-evolution</t>
+  </si>
+  <si>
+    <t>Visium HD prostate, one section</t>
+  </si>
+  <si>
+    <t>0.0326</t>
+  </si>
+  <si>
+    <t>0.9981</t>
+  </si>
+  <si>
+    <t>Extended Data 7g,h</t>
   </si>
   <si>
     <t>Depth of invasion, external</t>
@@ -269,9 +299,6 @@
     <t>TCGA-COAD, 65 evaluable slides</t>
   </si>
   <si>
-    <t>TLAgent-zeroshot</t>
-  </si>
-  <si>
     <t>pearson</t>
   </si>
   <si>
@@ -356,24 +383,33 @@
     <t>9.6478</t>
   </si>
   <si>
+    <t>0.6617</t>
+  </si>
+  <si>
+    <t>3.523</t>
+  </si>
+  <si>
+    <t>4.9687</t>
+  </si>
+  <si>
+    <t>Extended Data 7i</t>
+  </si>
+  <si>
+    <t>Depth of invasion, before and after co-evolution</t>
+  </si>
+  <si>
+    <t>LNCO2, 105 evaluable slides</t>
+  </si>
+  <si>
+    <t>0.5117</t>
+  </si>
+  <si>
+    <t>0.8425</t>
+  </si>
+  <si>
     <t>0.3909</t>
   </si>
   <si>
-    <t>4.2274</t>
-  </si>
-  <si>
-    <t>5.5652</t>
-  </si>
-  <si>
-    <t>0.6617</t>
-  </si>
-  <si>
-    <t>3.523</t>
-  </si>
-  <si>
-    <t>4.9687</t>
-  </si>
-  <si>
     <t>Extended Data 7j</t>
   </si>
   <si>
@@ -470,6 +506,9 @@
     <t>measurement_stack</t>
   </si>
   <si>
+    <t>system_description</t>
+  </si>
+  <si>
     <t>Extended Data 7k</t>
   </si>
   <si>
@@ -482,6 +521,30 @@
     <t>ADNI external</t>
   </si>
   <si>
+    <t>Reactive fraction</t>
+  </si>
+  <si>
+    <t>Reactive/astrogl. ratio 35µm</t>
+  </si>
+  <si>
+    <t>Peripyramidal react. 35µm</t>
+  </si>
+  <si>
+    <t>partial_pearson_r</t>
+  </si>
+  <si>
+    <t>donors</t>
+  </si>
+  <si>
+    <t>Archived SD across 100 repeated 80% donor subsamples; not a confidence interval</t>
+  </si>
+  <si>
+    <t>archived external-validation plotting input</t>
+  </si>
+  <si>
+    <t>NeuroFM</t>
+  </si>
+  <si>
     <t>Bulk reactive-astrocyte fraction</t>
   </si>
   <si>
@@ -489,21 +552,6 @@
   </si>
   <si>
     <t>Peripyramidal astrocyte-lineage reactivity, 35 um</t>
-  </si>
-  <si>
-    <t>partial_pearson_r</t>
-  </si>
-  <si>
-    <t>donors</t>
-  </si>
-  <si>
-    <t>Archived SD across 100 repeated 80% donor subsamples; not a confidence interval</t>
-  </si>
-  <si>
-    <t>archived external-validation plotting input</t>
-  </si>
-  <si>
-    <t>NeuroFM</t>
   </si>
 </sst>
 </file>
@@ -835,14 +883,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="48.7109375" customWidth="1"/>
     <col min="4" max="4" width="27.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -941,10 +989,10 @@
         <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -959,7 +1007,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -979,10 +1027,10 @@
         <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -997,7 +1045,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -1017,10 +1065,10 @@
         <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -1035,7 +1083,7 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -1055,10 +1103,10 @@
         <v>28</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -1073,22 +1121,22 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="N5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="U5">
         <v>0.0022</v>
@@ -1111,10 +1159,10 @@
         <v>28</v>
       </c>
       <c r="F6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -1129,22 +1177,22 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="U6">
         <v>569</v>
@@ -1167,10 +1215,10 @@
         <v>29</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1185,22 +1233,22 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M7">
-        <v>0.154</v>
+        <v>0.1394</v>
       </c>
       <c r="N7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="S7">
         <v>0.0173</v>
@@ -1232,10 +1280,10 @@
         <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1250,22 +1298,22 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M8">
         <v>40321.667</v>
       </c>
       <c r="N8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="S8">
         <v>4520</v>
@@ -1297,10 +1345,10 @@
         <v>30</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1315,22 +1363,22 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M9">
         <v>0.2561</v>
       </c>
       <c r="N9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R9">
         <v>0.831</v>
@@ -1365,10 +1413,10 @@
         <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -1383,22 +1431,22 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M10">
         <v>67067.9736</v>
       </c>
       <c r="N10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R10">
         <v>217638</v>
@@ -1433,10 +1481,10 @@
         <v>31</v>
       </c>
       <c r="F11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -1451,7 +1499,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1471,10 +1519,10 @@
         <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -1489,22 +1537,22 @@
         <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M12">
         <v>0</v>
       </c>
       <c r="N12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q12" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1539,10 +1587,10 @@
         <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -1557,22 +1605,22 @@
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M13">
         <v>4.4721</v>
       </c>
       <c r="N13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R13">
         <v>10</v>
@@ -1607,10 +1655,10 @@
         <v>33</v>
       </c>
       <c r="F14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -1625,22 +1673,22 @@
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="M14">
         <v>0.1709</v>
       </c>
       <c r="N14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R14">
         <v>0.4189</v>
@@ -1675,10 +1723,10 @@
         <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -1693,22 +1741,22 @@
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M15">
         <v>8564815.6874</v>
       </c>
       <c r="N15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R15">
         <v>109699</v>
@@ -1743,10 +1791,10 @@
         <v>34</v>
       </c>
       <c r="F16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -1761,37 +1809,37 @@
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M16">
         <v>0</v>
       </c>
       <c r="N16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R16">
-        <v>0.0017</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="S16">
-        <v>0.0017</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="T16">
-        <v>0.0017</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="U16">
-        <v>0.0017</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="V16">
-        <v>0.0017</v>
+        <v>0.9693000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -1811,10 +1859,10 @@
         <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -1829,37 +1877,37 @@
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R17">
-        <v>433</v>
+        <v>253870</v>
       </c>
       <c r="S17">
-        <v>433</v>
+        <v>253870</v>
       </c>
       <c r="T17">
-        <v>433</v>
+        <v>253870</v>
       </c>
       <c r="U17">
-        <v>433</v>
+        <v>253870</v>
       </c>
       <c r="V17">
-        <v>433</v>
+        <v>253870</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -1879,10 +1927,10 @@
         <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -1890,144 +1938,8 @@
       <c r="I18">
         <v>1</v>
       </c>
-      <c r="J18">
-        <v>5</v>
-      </c>
-      <c r="K18">
-        <v>5</v>
-      </c>
       <c r="L18" t="s">
-        <v>55</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
-        <v>58</v>
-      </c>
-      <c r="O18" t="s">
-        <v>58</v>
-      </c>
-      <c r="P18" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>58</v>
-      </c>
-      <c r="R18">
-        <v>0.9693000000000001</v>
-      </c>
-      <c r="S18">
-        <v>0.9693000000000001</v>
-      </c>
-      <c r="T18">
-        <v>0.9693000000000001</v>
-      </c>
-      <c r="U18">
-        <v>0.9693000000000001</v>
-      </c>
-      <c r="V18">
-        <v>0.9693000000000001</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" t="s">
-        <v>35</v>
-      </c>
-      <c r="F19" t="s">
-        <v>39</v>
-      </c>
-      <c r="G19" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19">
-        <v>1</v>
-      </c>
-      <c r="J19">
-        <v>5</v>
-      </c>
-      <c r="K19">
-        <v>5</v>
-      </c>
-      <c r="L19" t="s">
-        <v>56</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>58</v>
-      </c>
-      <c r="O19" t="s">
-        <v>58</v>
-      </c>
-      <c r="P19" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>58</v>
-      </c>
-      <c r="R19">
-        <v>253870</v>
-      </c>
-      <c r="S19">
-        <v>253870</v>
-      </c>
-      <c r="T19">
-        <v>253870</v>
-      </c>
-      <c r="U19">
-        <v>253870</v>
-      </c>
-      <c r="V19">
-        <v>253870</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" t="s">
-        <v>40</v>
-      </c>
-      <c r="G20" t="s">
-        <v>41</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="L20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2037,14 +1949,378 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="17" width="22.7109375" customWidth="1"/>
+    <col min="18" max="22" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>61</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2">
+        <v>0.0003</v>
+      </c>
+      <c r="S2">
+        <v>0.0003</v>
+      </c>
+      <c r="T2">
+        <v>0.0003</v>
+      </c>
+      <c r="U2">
+        <v>0.0003</v>
+      </c>
+      <c r="V2">
+        <v>0.0003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3">
+        <v>0.9487</v>
+      </c>
+      <c r="S3">
+        <v>0.9487</v>
+      </c>
+      <c r="T3">
+        <v>0.9487</v>
+      </c>
+      <c r="U3">
+        <v>0.9487</v>
+      </c>
+      <c r="V3">
+        <v>0.9487</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4">
+        <v>20</v>
+      </c>
+      <c r="B4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>63</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4">
+        <v>0.0017</v>
+      </c>
+      <c r="S4">
+        <v>0.0017</v>
+      </c>
+      <c r="T4">
+        <v>0.0017</v>
+      </c>
+      <c r="U4">
+        <v>0.0017</v>
+      </c>
+      <c r="V4">
+        <v>0.0017</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>52</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="S5">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="T5">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="U5">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="V5">
+        <v>0.9693000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:V19"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="45.7109375" customWidth="1"/>
     <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.7109375" customWidth="1"/>
     <col min="7" max="7" width="17.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -2129,22 +2405,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -2159,7 +2435,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -2167,22 +2443,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>26</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -2197,22 +2473,22 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M3">
         <v>0.0474</v>
       </c>
       <c r="N3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R3">
         <v>0.106</v>
@@ -2235,22 +2511,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -2265,22 +2541,22 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="M4">
         <v>2.2361</v>
       </c>
       <c r="N4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R4">
         <v>5</v>
@@ -2303,22 +2579,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -2333,22 +2609,22 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M5">
         <v>0</v>
       </c>
       <c r="N5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R5">
         <v>0.2121</v>
@@ -2371,22 +2647,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
         <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -2401,22 +2677,22 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="M6">
         <v>0</v>
       </c>
       <c r="N6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R6">
         <v>10</v>
@@ -2439,22 +2715,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -2469,7 +2745,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -2477,22 +2753,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E8" t="s">
         <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -2507,22 +2783,22 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="M8">
         <v>0.1209</v>
       </c>
       <c r="N8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R8">
         <v>0.3181</v>
@@ -2545,22 +2821,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
         <v>29</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -2575,22 +2851,22 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="M9">
         <v>5.7009</v>
       </c>
       <c r="N9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R9">
         <v>15</v>
@@ -2613,22 +2889,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E10" t="s">
         <v>30</v>
       </c>
       <c r="F10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -2643,22 +2919,22 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="M10">
         <v>0.0053</v>
       </c>
       <c r="N10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R10">
         <v>0.1845</v>
@@ -2681,22 +2957,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>30</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -2711,22 +2987,22 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M11">
         <v>0.251</v>
       </c>
       <c r="N11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R11">
         <v>8.699999999999999</v>
@@ -2749,22 +3025,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E12" t="s">
         <v>31</v>
       </c>
       <c r="F12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -2779,7 +3055,7 @@
         <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -2787,22 +3063,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
         <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -2817,22 +3093,22 @@
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="M13">
-        <v>0.002</v>
+        <v>0.0019</v>
       </c>
       <c r="N13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="S13">
         <v>0.0042</v>
@@ -2852,22 +3128,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C14" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
         <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -2882,22 +3158,22 @@
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="M14">
         <v>0.09569999999999999</v>
       </c>
       <c r="N14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q14" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="S14">
         <v>0.2</v>
@@ -2917,22 +3193,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D15" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -2947,22 +3223,22 @@
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="M15">
         <v>0.0319</v>
       </c>
       <c r="N15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R15">
         <v>0.0901</v>
@@ -2985,22 +3261,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D16" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E16" t="s">
         <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -3015,22 +3291,22 @@
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M16">
         <v>1.5058</v>
       </c>
       <c r="N16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R16">
         <v>4.25</v>
@@ -3053,22 +3329,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
         <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -3083,37 +3359,37 @@
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="M17">
         <v>0</v>
       </c>
       <c r="N17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>0.8927</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>0.8927</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>0.8927</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>0.8927</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>0.8927</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -3121,22 +3397,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D18" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E18" t="s">
         <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -3151,37 +3427,37 @@
         <v>5</v>
       </c>
       <c r="L18" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="M18">
         <v>0</v>
       </c>
       <c r="N18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="O18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="P18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="Q18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>42.09</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>42.09</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>42.09</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>42.09</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -3189,22 +3465,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D19" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
         <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="G19" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -3212,144 +3488,8 @@
       <c r="I19">
         <v>1</v>
       </c>
-      <c r="J19">
-        <v>5</v>
-      </c>
-      <c r="K19">
-        <v>5</v>
-      </c>
       <c r="L19" t="s">
-        <v>77</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" t="s">
-        <v>58</v>
-      </c>
-      <c r="O19" t="s">
-        <v>58</v>
-      </c>
-      <c r="P19" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>58</v>
-      </c>
-      <c r="R19">
-        <v>0.8927</v>
-      </c>
-      <c r="S19">
-        <v>0.8927</v>
-      </c>
-      <c r="T19">
-        <v>0.8927</v>
-      </c>
-      <c r="U19">
-        <v>0.8927</v>
-      </c>
-      <c r="V19">
-        <v>0.8927</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" t="s">
-        <v>61</v>
-      </c>
-      <c r="E20" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" t="s">
-        <v>41</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>1</v>
-      </c>
-      <c r="J20">
-        <v>5</v>
-      </c>
-      <c r="K20">
-        <v>5</v>
-      </c>
-      <c r="L20" t="s">
-        <v>78</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>58</v>
-      </c>
-      <c r="O20" t="s">
-        <v>58</v>
-      </c>
-      <c r="P20" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>58</v>
-      </c>
-      <c r="R20">
-        <v>42.09</v>
-      </c>
-      <c r="S20">
-        <v>42.09</v>
-      </c>
-      <c r="T20">
-        <v>42.09</v>
-      </c>
-      <c r="U20">
-        <v>42.09</v>
-      </c>
-      <c r="V20">
-        <v>42.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" t="s">
-        <v>63</v>
-      </c>
-      <c r="G21" t="s">
-        <v>41</v>
-      </c>
-      <c r="H21">
-        <v>1</v>
-      </c>
-      <c r="I21">
-        <v>1</v>
-      </c>
-      <c r="L21" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3357,16 +3497,380 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" customWidth="1"/>
+    <col min="4" max="4" width="33.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="17" width="22.7109375" customWidth="1"/>
+    <col min="18" max="22" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
+      <c r="A2">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" t="s">
+        <v>55</v>
+      </c>
+      <c r="P2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R2">
+        <v>0.0326</v>
+      </c>
+      <c r="S2">
+        <v>0.0326</v>
+      </c>
+      <c r="T2">
+        <v>0.0326</v>
+      </c>
+      <c r="U2">
+        <v>0.0326</v>
+      </c>
+      <c r="V2">
+        <v>0.0326</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>88</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>55</v>
+      </c>
+      <c r="O3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3">
+        <v>0.9981</v>
+      </c>
+      <c r="S3">
+        <v>0.9981</v>
+      </c>
+      <c r="T3">
+        <v>0.9981</v>
+      </c>
+      <c r="U3">
+        <v>0.9981</v>
+      </c>
+      <c r="V3">
+        <v>0.9981</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>48</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" t="s">
+        <v>55</v>
+      </c>
+      <c r="P4" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>55</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>81</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>55</v>
+      </c>
+      <c r="O5" t="s">
+        <v>55</v>
+      </c>
+      <c r="P5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>55</v>
+      </c>
+      <c r="R5">
+        <v>0.8927</v>
+      </c>
+      <c r="S5">
+        <v>0.8927</v>
+      </c>
+      <c r="T5">
+        <v>0.8927</v>
+      </c>
+      <c r="U5">
+        <v>0.8927</v>
+      </c>
+      <c r="V5">
+        <v>0.8927</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" customWidth="1"/>
     <col min="4" max="4" width="32.7109375" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -3436,22 +3940,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H2">
         <v>65</v>
@@ -3466,7 +3970,7 @@
         <v>5</v>
       </c>
       <c r="L2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:17">
@@ -3474,22 +3978,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E3" t="s">
         <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H3">
         <v>65</v>
@@ -3504,7 +4008,7 @@
         <v>5</v>
       </c>
       <c r="L3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:17">
@@ -3512,22 +4016,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
         <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H4">
         <v>65</v>
@@ -3542,7 +4046,7 @@
         <v>5</v>
       </c>
       <c r="L4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:17">
@@ -3550,22 +4054,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H5">
         <v>65</v>
@@ -3580,7 +4084,7 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="M5">
         <v>0.0321</v>
@@ -3603,22 +4107,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H6">
         <v>65</v>
@@ -3633,7 +4137,7 @@
         <v>5</v>
       </c>
       <c r="L6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M6">
         <v>0.06610000000000001</v>
@@ -3656,22 +4160,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E7" t="s">
         <v>26</v>
       </c>
       <c r="F7" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H7">
         <v>65</v>
@@ -3686,7 +4190,7 @@
         <v>5</v>
       </c>
       <c r="L7" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="M7">
         <v>0.0505</v>
@@ -3709,22 +4213,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H8">
         <v>65</v>
@@ -3739,7 +4243,7 @@
         <v>5</v>
       </c>
       <c r="L8" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="M8">
         <v>0.0596</v>
@@ -3762,22 +4266,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s">
         <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H9">
         <v>65</v>
@@ -3792,7 +4296,7 @@
         <v>5</v>
       </c>
       <c r="L9" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="M9">
         <v>0.197</v>
@@ -3815,22 +4319,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
         <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H10">
         <v>65</v>
@@ -3845,7 +4349,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="M10">
         <v>0.3019</v>
@@ -3868,22 +4372,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G11" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H11">
         <v>65</v>
@@ -3898,7 +4402,7 @@
         <v>5</v>
       </c>
       <c r="L11" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="M11">
         <v>0.155</v>
@@ -3921,22 +4425,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
       </c>
       <c r="F12" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G12" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H12">
         <v>65</v>
@@ -3951,7 +4455,7 @@
         <v>5</v>
       </c>
       <c r="L12" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="M12">
         <v>0.8099</v>
@@ -3974,22 +4478,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H13">
         <v>65</v>
@@ -4004,7 +4508,7 @@
         <v>5</v>
       </c>
       <c r="L13" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="M13">
         <v>0.9951</v>
@@ -4027,22 +4531,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
         <v>29</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H14">
         <v>65</v>
@@ -4057,7 +4561,7 @@
         <v>5</v>
       </c>
       <c r="L14" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="M14">
         <v>0.09619999999999999</v>
@@ -4080,22 +4584,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>29</v>
       </c>
       <c r="F15" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G15" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H15">
         <v>65</v>
@@ -4110,7 +4614,7 @@
         <v>5</v>
       </c>
       <c r="L15" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M15">
         <v>0.1439</v>
@@ -4133,22 +4637,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
         <v>29</v>
       </c>
       <c r="F16" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H16">
         <v>65</v>
@@ -4163,7 +4667,7 @@
         <v>5</v>
       </c>
       <c r="L16" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="M16">
         <v>0.1953</v>
@@ -4186,22 +4690,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E17" t="s">
         <v>30</v>
       </c>
       <c r="F17" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H17">
         <v>65</v>
@@ -4216,7 +4720,7 @@
         <v>5</v>
       </c>
       <c r="L17" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M17">
         <v>0.0557</v>
@@ -4239,22 +4743,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D18" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E18" t="s">
         <v>30</v>
       </c>
       <c r="F18" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H18">
         <v>65</v>
@@ -4269,7 +4773,7 @@
         <v>5</v>
       </c>
       <c r="L18" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="M18">
         <v>0.164</v>
@@ -4292,22 +4796,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E19" t="s">
         <v>30</v>
       </c>
       <c r="F19" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H19">
         <v>65</v>
@@ -4322,7 +4826,7 @@
         <v>5</v>
       </c>
       <c r="L19" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="M19">
         <v>0.097</v>
@@ -4345,22 +4849,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D20" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E20" t="s">
         <v>31</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G20" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H20">
         <v>65</v>
@@ -4375,7 +4879,7 @@
         <v>5</v>
       </c>
       <c r="L20" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="M20">
         <v>0.1615</v>
@@ -4398,22 +4902,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E21" t="s">
         <v>31</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H21">
         <v>65</v>
@@ -4428,7 +4932,7 @@
         <v>5</v>
       </c>
       <c r="L21" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M21">
         <v>0.7654</v>
@@ -4451,22 +4955,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
         <v>31</v>
       </c>
       <c r="F22" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G22" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H22">
         <v>65</v>
@@ -4481,7 +4985,7 @@
         <v>5</v>
       </c>
       <c r="L22" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="M22">
         <v>0.8335</v>
@@ -4504,22 +5008,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E23" t="s">
         <v>32</v>
       </c>
       <c r="F23" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H23">
         <v>65</v>
@@ -4534,7 +5038,7 @@
         <v>5</v>
       </c>
       <c r="L23" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="M23">
         <v>0.1423</v>
@@ -4557,22 +5061,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E24" t="s">
         <v>32</v>
       </c>
       <c r="F24" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H24">
         <v>65</v>
@@ -4587,7 +5091,7 @@
         <v>5</v>
       </c>
       <c r="L24" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="M24">
         <v>3.1573</v>
@@ -4610,22 +5114,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C25" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E25" t="s">
         <v>32</v>
       </c>
       <c r="F25" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H25">
         <v>65</v>
@@ -4640,7 +5144,7 @@
         <v>5</v>
       </c>
       <c r="L25" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M25">
         <v>22.0312</v>
@@ -4663,22 +5167,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D26" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
         <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G26" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H26">
         <v>65</v>
@@ -4693,7 +5197,7 @@
         <v>5</v>
       </c>
       <c r="L26" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="M26">
         <v>0.09080000000000001</v>
@@ -4716,22 +5220,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C27" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D27" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E27" t="s">
         <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G27" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H27">
         <v>65</v>
@@ -4746,7 +5250,7 @@
         <v>5</v>
       </c>
       <c r="L27" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="M27">
         <v>0.4753</v>
@@ -4769,22 +5273,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D28" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
         <v>33</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G28" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H28">
         <v>65</v>
@@ -4799,7 +5303,7 @@
         <v>5</v>
       </c>
       <c r="L28" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="M28">
         <v>0.4472</v>
@@ -4822,22 +5326,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D29" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="F29" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H29">
         <v>65</v>
@@ -4852,22 +5356,22 @@
         <v>5</v>
       </c>
       <c r="L29" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="M29">
         <v>0</v>
       </c>
       <c r="N29">
-        <v>0.19</v>
+        <v>0.5289</v>
       </c>
       <c r="O29">
-        <v>0.5736</v>
+        <v>0.7739</v>
       </c>
       <c r="P29">
-        <v>0.1916</v>
+        <v>0.5189</v>
       </c>
       <c r="Q29">
-        <v>0.571</v>
+        <v>0.7758</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -4875,22 +5379,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D30" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E30" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H30">
         <v>65</v>
@@ -4905,22 +5409,22 @@
         <v>5</v>
       </c>
       <c r="L30" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="M30">
         <v>0</v>
       </c>
       <c r="N30">
-        <v>3.3794</v>
+        <v>2.7185</v>
       </c>
       <c r="O30">
-        <v>5.1361</v>
+        <v>4.3955</v>
       </c>
       <c r="P30">
-        <v>3.3884</v>
+        <v>2.6963</v>
       </c>
       <c r="Q30">
-        <v>5.129</v>
+        <v>4.4162</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -4928,22 +5432,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="E31" t="s">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="F31" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G31" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H31">
         <v>65</v>
@@ -4958,180 +5462,21 @@
         <v>5</v>
       </c>
       <c r="L31" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M31">
         <v>0</v>
       </c>
       <c r="N31">
-        <v>4.5098</v>
+        <v>3.9175</v>
       </c>
       <c r="O31">
-        <v>6.5596</v>
+        <v>5.9511</v>
       </c>
       <c r="P31">
-        <v>4.5113</v>
+        <v>3.8877</v>
       </c>
       <c r="Q31">
-        <v>6.5695</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" t="s">
-        <v>82</v>
-      </c>
-      <c r="E32" t="s">
-        <v>35</v>
-      </c>
-      <c r="F32" t="s">
-        <v>84</v>
-      </c>
-      <c r="G32" t="s">
-        <v>87</v>
-      </c>
-      <c r="H32">
-        <v>65</v>
-      </c>
-      <c r="I32">
-        <v>63</v>
-      </c>
-      <c r="J32">
-        <v>65</v>
-      </c>
-      <c r="K32">
-        <v>5</v>
-      </c>
-      <c r="L32" t="s">
-        <v>115</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0.5289</v>
-      </c>
-      <c r="O32">
-        <v>0.7739</v>
-      </c>
-      <c r="P32">
-        <v>0.5189</v>
-      </c>
-      <c r="Q32">
-        <v>0.7758</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" t="s">
-        <v>35</v>
-      </c>
-      <c r="F33" t="s">
-        <v>85</v>
-      </c>
-      <c r="G33" t="s">
-        <v>87</v>
-      </c>
-      <c r="H33">
-        <v>65</v>
-      </c>
-      <c r="I33">
-        <v>63</v>
-      </c>
-      <c r="J33">
-        <v>65</v>
-      </c>
-      <c r="K33">
-        <v>5</v>
-      </c>
-      <c r="L33" t="s">
-        <v>116</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="N33">
-        <v>2.7185</v>
-      </c>
-      <c r="O33">
-        <v>4.3955</v>
-      </c>
-      <c r="P33">
-        <v>2.6963</v>
-      </c>
-      <c r="Q33">
-        <v>4.4162</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" t="s">
-        <v>35</v>
-      </c>
-      <c r="F34" t="s">
-        <v>86</v>
-      </c>
-      <c r="G34" t="s">
-        <v>87</v>
-      </c>
-      <c r="H34">
-        <v>65</v>
-      </c>
-      <c r="I34">
-        <v>63</v>
-      </c>
-      <c r="J34">
-        <v>65</v>
-      </c>
-      <c r="K34">
-        <v>5</v>
-      </c>
-      <c r="L34" t="s">
-        <v>117</v>
-      </c>
-      <c r="M34">
-        <v>0</v>
-      </c>
-      <c r="N34">
-        <v>3.9175</v>
-      </c>
-      <c r="O34">
-        <v>5.9511</v>
-      </c>
-      <c r="P34">
-        <v>3.8877</v>
-      </c>
-      <c r="Q34">
         <v>5.9735</v>
       </c>
     </row>
@@ -5140,7 +5485,296 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="4" max="4" width="32.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="10" width="12.7109375" customWidth="1"/>
+    <col min="11" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" customWidth="1"/>
+    <col min="16" max="17" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H2">
+        <v>105</v>
+      </c>
+      <c r="I2">
+        <v>43</v>
+      </c>
+      <c r="J2">
+        <v>105</v>
+      </c>
+      <c r="K2">
+        <v>5</v>
+      </c>
+      <c r="L2" t="s">
+        <v>126</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0.365</v>
+      </c>
+      <c r="O2">
+        <v>0.6598000000000001</v>
+      </c>
+      <c r="P2">
+        <v>0.3494</v>
+      </c>
+      <c r="Q2">
+        <v>0.6676</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3">
+        <v>32</v>
+      </c>
+      <c r="B3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3">
+        <v>105</v>
+      </c>
+      <c r="I3">
+        <v>43</v>
+      </c>
+      <c r="J3">
+        <v>105</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>127</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0.7233000000000001</v>
+      </c>
+      <c r="O3">
+        <v>0.9124</v>
+      </c>
+      <c r="P3">
+        <v>0.7025</v>
+      </c>
+      <c r="Q3">
+        <v>0.9193</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G4" t="s">
+        <v>95</v>
+      </c>
+      <c r="H4">
+        <v>65</v>
+      </c>
+      <c r="I4">
+        <v>63</v>
+      </c>
+      <c r="J4">
+        <v>65</v>
+      </c>
+      <c r="K4">
+        <v>5</v>
+      </c>
+      <c r="L4" t="s">
+        <v>128</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0.19</v>
+      </c>
+      <c r="O4">
+        <v>0.5736</v>
+      </c>
+      <c r="P4">
+        <v>0.1916</v>
+      </c>
+      <c r="Q4">
+        <v>0.571</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" t="s">
+        <v>124</v>
+      </c>
+      <c r="D5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
+        <v>92</v>
+      </c>
+      <c r="G5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5">
+        <v>65</v>
+      </c>
+      <c r="I5">
+        <v>63</v>
+      </c>
+      <c r="J5">
+        <v>65</v>
+      </c>
+      <c r="K5">
+        <v>5</v>
+      </c>
+      <c r="L5" t="s">
+        <v>120</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0.5289</v>
+      </c>
+      <c r="O5">
+        <v>0.7739</v>
+      </c>
+      <c r="P5">
+        <v>0.5189</v>
+      </c>
+      <c r="Q5">
+        <v>0.7758</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5217,22 +5851,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H2">
         <v>30</v>
@@ -5258,22 +5892,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F3" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H3">
         <v>30</v>
@@ -5299,22 +5933,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E4" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F4" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H4">
         <v>30</v>
@@ -5340,22 +5974,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E5" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F5" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G5" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H5">
         <v>30</v>
@@ -5381,22 +6015,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D6" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E6" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F6" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H6">
         <v>30</v>
@@ -5422,22 +6056,22 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C7" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E7" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F7" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G7" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H7">
         <v>30</v>
@@ -5463,22 +6097,22 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D8" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F8" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G8" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H8">
         <v>30</v>
@@ -5504,22 +6138,22 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D9" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F9" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G9" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H9">
         <v>30</v>
@@ -5545,22 +6179,22 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D10" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F10" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H10">
         <v>30</v>
@@ -5586,22 +6220,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E11" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F11" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G11" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H11">
         <v>30</v>
@@ -5627,22 +6261,22 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D12" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E12" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F12" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G12" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H12">
         <v>30</v>
@@ -5668,22 +6302,22 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E13" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F13" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G13" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H13">
         <v>30</v>
@@ -5709,22 +6343,22 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D14" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="F14" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H14">
         <v>30</v>
@@ -5750,22 +6384,22 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E15" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F15" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G15" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H15">
         <v>30</v>
@@ -5791,22 +6425,22 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D16" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E16" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F16" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G16" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H16">
         <v>30</v>
@@ -5832,22 +6466,22 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D17" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E17" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F17" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G17" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H17">
         <v>30</v>
@@ -5873,22 +6507,22 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="F18" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G18" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H18">
         <v>30</v>
@@ -5914,22 +6548,22 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E19" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F19" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G19" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H19">
         <v>30</v>
@@ -5955,22 +6589,22 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D20" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E20" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="F20" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G20" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H20">
         <v>30</v>
@@ -5996,22 +6630,22 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="E21" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F21" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G21" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H21">
         <v>30</v>
@@ -6037,22 +6671,22 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C22" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E22" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="F22" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G22" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H22">
         <v>75</v>
@@ -6078,22 +6712,22 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D23" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E23" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="F23" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H23">
         <v>75</v>
@@ -6119,22 +6753,22 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C24" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F24" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G24" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H24">
         <v>75</v>
@@ -6160,22 +6794,22 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D25" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E25" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="F25" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G25" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H25">
         <v>75</v>
@@ -6201,22 +6835,22 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D26" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F26" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G26" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H26">
         <v>75</v>
@@ -6242,22 +6876,22 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F27" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G27" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H27">
         <v>75</v>
@@ -6283,22 +6917,22 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C28" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E28" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F28" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G28" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H28">
         <v>75</v>
@@ -6324,22 +6958,22 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D29" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E29" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="F29" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G29" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H29">
         <v>75</v>
@@ -6365,22 +6999,22 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D30" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E30" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F30" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G30" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H30">
         <v>75</v>
@@ -6406,22 +7040,22 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D31" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E31" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F31" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G31" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H31">
         <v>75</v>
@@ -6447,22 +7081,22 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D32" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E32" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F32" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G32" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H32">
         <v>75</v>
@@ -6488,22 +7122,22 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C33" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E33" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F33" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G33" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H33">
         <v>75</v>
@@ -6529,22 +7163,22 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C34" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E34" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="F34" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G34" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H34">
         <v>75</v>
@@ -6570,22 +7204,22 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E35" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F35" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G35" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H35">
         <v>75</v>
@@ -6611,22 +7245,22 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E36" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F36" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G36" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H36">
         <v>75</v>
@@ -6652,22 +7286,22 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C37" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D37" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F37" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G37" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H37">
         <v>75</v>
@@ -6693,22 +7327,22 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C38" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D38" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="F38" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G38" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H38">
         <v>75</v>
@@ -6734,22 +7368,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E39" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="F39" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G39" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H39">
         <v>75</v>
@@ -6775,22 +7409,22 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E40" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="F40" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G40" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H40">
         <v>75</v>
@@ -6816,22 +7450,22 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C41" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="E41" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="F41" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G41" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="H41">
         <v>75</v>
@@ -6857,16 +7491,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" customWidth="1"/>
     <col min="4" max="4" width="17.7109375" customWidth="1"/>
-    <col min="5" max="5" width="55.7109375" customWidth="1"/>
+    <col min="5" max="5" width="30.7109375" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" customWidth="1"/>
     <col min="8" max="8" width="10.7109375" customWidth="1"/>
@@ -6882,9 +7516,10 @@
     <col min="21" max="21" width="60.7109375" customWidth="1"/>
     <col min="22" max="22" width="45.7109375" customWidth="1"/>
     <col min="23" max="23" width="19.7109375" customWidth="1"/>
+    <col min="24" max="24" width="55.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:24">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6937,45 +7572,48 @@
         <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="S1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="T1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="U1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="V1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="W1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23">
+        <v>160</v>
+      </c>
+      <c r="X1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C2" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F2" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H2">
         <v>34</v>
@@ -7002,36 +7640,39 @@
         <v>0.8</v>
       </c>
       <c r="U2" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="V2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="W2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23">
+        <v>173</v>
+      </c>
+      <c r="X2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="E3" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F3" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H3">
         <v>56</v>
@@ -7058,36 +7699,39 @@
         <v>0.8</v>
       </c>
       <c r="U3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="V3" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="W3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
+        <v>173</v>
+      </c>
+      <c r="X3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C4" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D4" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E4" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="F4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G4" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H4">
         <v>34</v>
@@ -7114,36 +7758,39 @@
         <v>0.8</v>
       </c>
       <c r="U4" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="V4" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="W4" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23">
+        <v>173</v>
+      </c>
+      <c r="X4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="E5" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="F5" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G5" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H5">
         <v>56</v>
@@ -7170,36 +7817,39 @@
         <v>0.8</v>
       </c>
       <c r="U5" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="V5" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="W5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
+        <v>173</v>
+      </c>
+      <c r="X5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C6" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D6" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="E6" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F6" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G6" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H6">
         <v>34</v>
@@ -7226,36 +7876,39 @@
         <v>0.8</v>
       </c>
       <c r="U6" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="V6" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="W6" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
+        <v>173</v>
+      </c>
+      <c r="X6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C7" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D7" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="E7" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="F7" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="G7" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="H7">
         <v>56</v>
@@ -7282,13 +7935,16 @@
         <v>0.8</v>
       </c>
       <c r="U7" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="V7" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="W7" t="s">
-        <v>161</v>
+        <v>173</v>
+      </c>
+      <c r="X7" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
